--- a/safety_inspection_forms/013_fire_safety_equipment_test_request_form--safety_inspection_forms.xlsx
+++ b/safety_inspection_forms/013_fire_safety_equipment_test_request_form--safety_inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fire_extinguisher</t>
+          <t>fire extinguisher</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fire_exinguisher</t>
+          <t>fire exinguisher</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fire_exinguisher</t>
+          <t>fire exinguisher</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>fire_exinguisher</t>
+          <t>fire exinguisher</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>fire_exinguisher</t>
+          <t>fire exinguisher</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>fire_exinguisher</t>
+          <t>fire exinguisher</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>fire_exinguisher</t>
+          <t>fire exinguisher</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>fire_exinguisher</t>
+          <t>fire exinguisher</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>fire_exinguisher</t>
+          <t>fire exinguisher</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>fire_exinguisher</t>
+          <t>fire exinguisher</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>fire_exinguisher</t>
+          <t>fire exinguisher</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>fire_exinguisher</t>
+          <t>fire exinguisher</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>fire_exinguisher</t>
+          <t>fire exinguisher</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>fire_exinguisher</t>
+          <t>fire exinguisher</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>fire_exinguisher</t>
+          <t>fire exinguisher</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>fire_exinguisher</t>
+          <t>fire exinguisher</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>fire_exinguisher</t>
+          <t>fire exinguisher</t>
         </is>
       </c>
     </row>
